--- a/Result/profitability/2027.xlsx
+++ b/Result/profitability/2027.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6975</v>
+        <v>0.9225</v>
       </c>
       <c r="N2" t="n">
-        <v>22.99375</v>
+        <v>24.3775</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.82</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7837499999999999</v>
+        <v>0.9575</v>
       </c>
       <c r="N3" t="n">
-        <v>22.6225</v>
+        <v>24.0175</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7062499999999999</v>
+        <v>0.86375</v>
       </c>
       <c r="N4" t="n">
-        <v>21.17</v>
+        <v>22.1425</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-8.619999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.455</v>
+        <v>-0.2662499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.116249999999999</v>
+        <v>8.883750000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.47875</v>
+        <v>-0.3624999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>6.989999999999999</v>
+        <v>7.50625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5975</v>
+        <v>-0.4562499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>5.84875</v>
+        <v>6.46625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.34</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.655</v>
+        <v>-0.5599999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>5.508749999999999</v>
+        <v>5.905</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>0.03</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7975</v>
+        <v>-0.7974999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>4.50625</v>
+        <v>4.506250000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.37</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8574999999999999</v>
+        <v>-0.8574999999999998</v>
       </c>
       <c r="N10" t="n">
         <v>4.3325</v>
@@ -1772,7 +1772,7 @@
         <v>0.42</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9075</v>
+        <v>-0.9074999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>4.66375</v>
@@ -1899,10 +1899,10 @@
         <v>0.24</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8674999999999999</v>
+        <v>-0.8674999999999998</v>
       </c>
       <c r="N12" t="n">
-        <v>5.45125</v>
+        <v>5.451250000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>0.22</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2374999999999999</v>
+        <v>0.2375</v>
       </c>
       <c r="N13" t="n">
         <v>17.73625</v>
@@ -9335,16 +9335,16 @@
         <v>25414</v>
       </c>
       <c r="D71" t="n">
-        <v>19229</v>
+        <v>19227</v>
       </c>
       <c r="E71" t="n">
-        <v>6185</v>
+        <v>6188</v>
       </c>
       <c r="F71" t="n">
-        <v>24.34</v>
+        <v>24.35</v>
       </c>
       <c r="G71" t="n">
-        <v>3511</v>
+        <v>3513</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -9355,10 +9355,10 @@
         <v>-1668</v>
       </c>
       <c r="J71" t="n">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="K71" t="n">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="L71" t="n">
         <v>0.42</v>
@@ -9367,7 +9367,7 @@
         <v>0.4225</v>
       </c>
       <c r="N71" t="n">
-        <v>19.70625</v>
+        <v>19.7075</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -9400,10 +9400,10 @@
         <v>-0.373134328358209</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.629999999999999</v>
+        <v>1.640000000000001</v>
       </c>
       <c r="Z71" t="n">
-        <v>0.07177454865697919</v>
+        <v>0.07221488331131654</v>
       </c>
       <c r="AA71" t="n">
         <v>0.01999999999999996</v>
@@ -9412,10 +9412,10 @@
         <v>0.04999999999999982</v>
       </c>
       <c r="AC71" t="n">
-        <v>4.600000000000001</v>
+        <v>4.610000000000003</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.2330293819655522</v>
+        <v>0.2335359675785209</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -9462,16 +9462,16 @@
         <v>25864</v>
       </c>
       <c r="D72" t="n">
-        <v>19046</v>
+        <v>19048</v>
       </c>
       <c r="E72" t="n">
-        <v>6819</v>
+        <v>6816</v>
       </c>
       <c r="F72" t="n">
-        <v>26.36</v>
+        <v>26.35</v>
       </c>
       <c r="G72" t="n">
-        <v>4023</v>
+        <v>4021</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -9482,10 +9482,10 @@
         <v>-289</v>
       </c>
       <c r="J72" t="n">
-        <v>3734</v>
+        <v>3732</v>
       </c>
       <c r="K72" t="n">
-        <v>2316</v>
+        <v>2314</v>
       </c>
       <c r="L72" t="n">
         <v>1</v>
@@ -9527,10 +9527,10 @@
         <v>1.380952380952381</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.0829909613804436</v>
+        <v>0.08213552361396292</v>
       </c>
       <c r="AA72" t="n">
         <v>0.87</v>
@@ -9539,10 +9539,10 @@
         <v>6.692307692307692</v>
       </c>
       <c r="AC72" t="n">
-        <v>6.939999999999998</v>
+        <v>6.93</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.3573635427394437</v>
+        <v>0.3568486096807415</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -9654,10 +9654,10 @@
         <v>-0.2</v>
       </c>
       <c r="Y73" t="n">
-        <v>-0.8099999999999987</v>
+        <v>-0.8000000000000007</v>
       </c>
       <c r="Z73" t="n">
-        <v>-0.03072837632776926</v>
+        <v>-0.03036053130929794</v>
       </c>
       <c r="AA73" t="n">
         <v>0.26</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>35998</v>
+      </c>
+      <c r="D75" t="n">
+        <v>25022</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10976</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="G75" t="n">
+        <v>7598</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>21.11%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>181</v>
+      </c>
+      <c r="J75" t="n">
+        <v>7779</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4786</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6495726495726497</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.169999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1160322108345533</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.595238095238095</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.139999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2521560574948665</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
